--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{115BC1E5-EA54-405B-B462-A41091A703DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD1DDE79-52CC-439D-8CE1-58458255BC03}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E329FD5D-E5C9-4634-A7E7-F96A7B766132}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D89D644B-7592-44C6-8571-D650E1D91494}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB71F9C8-A8B7-404C-9973-CB88E2C9B346}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6916D2A7-0BD1-467F-8D6B-78C73601394C}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD1DDE79-52CC-439D-8CE1-58458255BC03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0A83F9C-C6F9-4AE9-8CD1-6EE7FCD5AEBF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D89D644B-7592-44C6-8571-D650E1D91494}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A829748-103C-46E4-9829-00A51FB0FE10}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6916D2A7-0BD1-467F-8D6B-78C73601394C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{261D9C80-78B5-4275-AFD7-0D97D84C4A89}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0A83F9C-C6F9-4AE9-8CD1-6EE7FCD5AEBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8F3E0E-B485-4A0C-8D43-83E42F7A1182}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A829748-103C-46E4-9829-00A51FB0FE10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16801BA1-5ED1-4381-82AC-D342E559192A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{261D9C80-78B5-4275-AFD7-0D97D84C4A89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EAC822D-7C5B-4E02-9F4A-CF521871C2F6}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8F3E0E-B485-4A0C-8D43-83E42F7A1182}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCB650EF-C255-445C-A16A-45A021C4E6B0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16801BA1-5ED1-4381-82AC-D342E559192A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9F237A3-5EE4-4F54-959C-84ED3ED3CF51}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EAC822D-7C5B-4E02-9F4A-CF521871C2F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{954276E5-521D-4D1B-95C6-18C6651E68CE}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -11,6 +11,212 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Species Generic Name</t>
+  </si>
+  <si>
+    <t>Depth</t>
+  </si>
+  <si>
+    <t>Depth_Ref</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Length_Ref</t>
+  </si>
+  <si>
+    <t>Arboreality</t>
+  </si>
+  <si>
+    <t>Diet</t>
+  </si>
+  <si>
+    <t>Hand–eye</t>
+  </si>
+  <si>
+    <t>Ateles ater</t>
+  </si>
+  <si>
+    <t>Spider monkey</t>
+  </si>
+  <si>
+    <t>Canis latrans</t>
+  </si>
+  <si>
+    <t>Canis familiaris</t>
+  </si>
+  <si>
+    <t>Dog</t>
+  </si>
+  <si>
+    <t>Capra hircus</t>
+  </si>
+  <si>
+    <t>Goat</t>
+  </si>
+  <si>
+    <t>Sapajus apella</t>
+  </si>
+  <si>
+    <t>Cebus apella</t>
+  </si>
+  <si>
+    <t>Capuchin monkey</t>
+  </si>
+  <si>
+    <t>Chlorocebus sabaeus</t>
+  </si>
+  <si>
+    <t>Cercopithecus pygerythrus</t>
+  </si>
+  <si>
+    <t>Vervet</t>
+  </si>
+  <si>
+    <t>Dasypus novemcinctus</t>
+  </si>
+  <si>
+    <t>Nine-banded armadillo</t>
+  </si>
+  <si>
+    <t>Didelphis virginiana</t>
+  </si>
+  <si>
+    <t>Virginia opossum</t>
+  </si>
+  <si>
+    <t>Felis catus</t>
+  </si>
+  <si>
+    <t>Felis domesticus</t>
+  </si>
+  <si>
+    <t>Cat</t>
+  </si>
+  <si>
+    <t>Otolemur garnettii</t>
+  </si>
+  <si>
+    <t>Galago crassicaudatus</t>
+  </si>
+  <si>
+    <t>Greater bushbaby</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Human</t>
+  </si>
+  <si>
+    <t>Hylobates lar</t>
+  </si>
+  <si>
+    <t>Gibbon</t>
+  </si>
+  <si>
+    <t>Lagothrix lagotricha</t>
+  </si>
+  <si>
+    <t>Woolly monkey</t>
+  </si>
+  <si>
+    <t>Macaca mulatta</t>
+  </si>
+  <si>
+    <t>Rhesus macaque</t>
+  </si>
+  <si>
+    <t>Myocastor coypus</t>
+  </si>
+  <si>
+    <t>Coypu</t>
+  </si>
+  <si>
+    <t>Nycticebus coucang</t>
+  </si>
+  <si>
+    <t>Slow  loris</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Chimpanzee</t>
+  </si>
+  <si>
+    <t>Potorous tridactylus</t>
+  </si>
+  <si>
+    <t>Potoroo</t>
+  </si>
+  <si>
+    <t>Potos flavus</t>
+  </si>
+  <si>
+    <t>Kinkajou</t>
+  </si>
+  <si>
+    <t>Procyon lotor</t>
+  </si>
+  <si>
+    <t>Raccoon</t>
+  </si>
+  <si>
+    <t>Rattus norvegicus</t>
+  </si>
+  <si>
+    <t>Norway rat</t>
+  </si>
+  <si>
+    <t>Saguinus oedipus</t>
+  </si>
+  <si>
+    <t>Cotton-top marmoset</t>
+  </si>
+  <si>
+    <t>Saimiri boliviensis boliviensis</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Squirrel monkey</t>
+  </si>
+  <si>
+    <t>Setonix brachyurus</t>
+  </si>
+  <si>
+    <t>Quokka</t>
+  </si>
+  <si>
+    <t>Trichosurus vulpecula</t>
+  </si>
+  <si>
+    <t>Brush-tailed possum</t>
+  </si>
+  <si>
+    <t>Tupaia belangeri</t>
+  </si>
+  <si>
+    <t>Tupaia glis</t>
+  </si>
+  <si>
+    <t>Tree shrew</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,68 +560,44 @@
   <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Species Generic Name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Depth_Ref</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Length_Ref</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Arboreality</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Diet</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Hand–eye</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ateles ater</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Spider monkey</t>
-        </is>
+    <row r="1" spans="1:10" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -439,21 +621,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Canis latrans</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Canis familiaris</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Dog</t>
-        </is>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -477,16 +653,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Capra hircus</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Goat</t>
-        </is>
+    <row r="4" spans="1:10">
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -510,21 +682,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Cebus apella</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Capuchin monkey</t>
-        </is>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -548,21 +714,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chlorocebus sabaeus</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cercopithecus pygerythrus</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Vervet</t>
-        </is>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -586,21 +746,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Dasypus novemcinctus</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Dasypus novemcinctus</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Nine-banded armadillo</t>
-        </is>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -624,16 +778,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Didelphis virginiana</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Virginia opossum</t>
-        </is>
+    <row r="8" spans="1:10">
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -657,21 +807,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Felis catus</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Felis domesticus</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -695,21 +839,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Otolemur garnettii</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Galago crassicaudatus</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Greater bushbaby</t>
-        </is>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -733,21 +871,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -771,16 +903,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Gibbon</t>
-        </is>
+    <row r="12" spans="1:10">
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -804,16 +932,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Lagothrix lagotricha</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Woolly monkey</t>
-        </is>
+    <row r="13" spans="1:10">
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -837,21 +961,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Rhesus macaque</t>
-        </is>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -875,16 +993,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Myocastor coypus</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Coypu</t>
-        </is>
+    <row r="15" spans="1:10">
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -908,16 +1022,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Nycticebus coucang</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Slow  loris</t>
-        </is>
+    <row r="16" spans="1:10">
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -941,21 +1051,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Chimpanzee</t>
-        </is>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -979,16 +1083,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Potorous tridactylus</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Potoroo</t>
-        </is>
+    <row r="18" spans="1:10">
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1012,16 +1112,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Potos flavus</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Kinkajou</t>
-        </is>
+    <row r="19" spans="1:10">
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -1045,16 +1141,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Procyon lotor</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Raccoon</t>
-        </is>
+    <row r="20" spans="1:10">
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -1078,21 +1170,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Norway rat</t>
-        </is>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1116,16 +1202,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Cotton-top marmoset</t>
-        </is>
+    <row r="22" spans="1:10">
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" t="s">
+        <v>56</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1149,21 +1231,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Saimiri boliviensis boliviensis</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Squirrel monkey</t>
-        </is>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -1187,16 +1263,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Setonix brachyurus</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Quokka</t>
-        </is>
+    <row r="24" spans="1:10">
+      <c r="B24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
+        <v>61</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1220,16 +1292,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Trichosurus vulpecula</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brush-tailed possum</t>
-        </is>
+    <row r="25" spans="1:10">
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>63</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -1253,21 +1321,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Tupaia belangeri</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Tupaia glis</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Tree shrew</t>
-        </is>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>66</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1572,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCB650EF-C255-445C-A16A-45A021C4E6B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{093A5FD3-CB40-42D4-97BF-B911704CD863}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9F237A3-5EE4-4F54-959C-84ED3ED3CF51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1B71576-C0DA-4025-AB60-B2572E3F4F4B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{954276E5-521D-4D1B-95C6-18C6651E68CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04A763A8-9F57-4071-9AC8-7B43E3ED51BA}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{093A5FD3-CB40-42D4-97BF-B911704CD863}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA524FA1-003F-4F90-BE9B-A767C6A078FE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1B71576-C0DA-4025-AB60-B2572E3F4F4B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69B08870-50D3-4EC0-93D1-2C2EF1BFE4C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04A763A8-9F57-4071-9AC8-7B43E3ED51BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0F1B940-90D9-4BA7-A494-7B2FC9D227DB}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA524FA1-003F-4F90-BE9B-A767C6A078FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07FACB2E-BEE9-4EE2-9D37-AFDC03B13A32}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69B08870-50D3-4EC0-93D1-2C2EF1BFE4C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{284BCF80-B48E-4FE3-9691-E48399CFA606}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0F1B940-90D9-4BA7-A494-7B2FC9D227DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FCC7CAE-C930-4F13-8DE9-520E1BB6E2B2}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1356,291 +1356,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07FACB2E-BEE9-4EE2-9D37-AFDC03B13A32}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{284BCF80-B48E-4FE3-9691-E48399CFA606}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FCC7CAE-C930-4F13-8DE9-520E1BB6E2B2}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1356,4 +1356,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B040C0F6-EDB8-482E-8E4C-3924A22AAD67}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64FFC839-820E-42F5-A898-77757047475D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D25A8ED2-84A5-4757-A69C-02901D1433A3}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1356,291 +1356,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B040C0F6-EDB8-482E-8E4C-3924A22AAD67}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64FFC839-820E-42F5-A898-77757047475D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D25A8ED2-84A5-4757-A69C-02901D1433A3}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1356,4 +1356,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87377449-EB5E-4662-8009-82B7BA581AFD}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6562E965-227E-45FD-B48F-A01D060936DC}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56630F73-710C-489D-AB8B-F25BD0EC5F14}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87377449-EB5E-4662-8009-82B7BA581AFD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FBDEC2C-3229-4C18-8D23-276E38271C33}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6562E965-227E-45FD-B48F-A01D060936DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DBE1A06-2010-4691-89D8-A4CECB74A673}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56630F73-710C-489D-AB8B-F25BD0EC5F14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015FF4CD-38FC-488A-8B53-863E5038A3A4}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FBDEC2C-3229-4C18-8D23-276E38271C33}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76C1EAB4-DF52-4A51-A573-CE3E21EB7E1E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DBE1A06-2010-4691-89D8-A4CECB74A673}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BAB4BC1-5F70-438D-BEB6-9573C44279AA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015FF4CD-38FC-488A-8B53-863E5038A3A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FFDD86F-7104-4707-A3F3-1209FE4E63CE}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76C1EAB4-DF52-4A51-A573-CE3E21EB7E1E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62E3ECD6-B146-4072-A5FF-DA34DDBC6681}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BAB4BC1-5F70-438D-BEB6-9573C44279AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71DF8E51-F87F-412A-BA7B-3623376C6A25}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FFDD86F-7104-4707-A3F3-1209FE4E63CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F38B105C-4DED-43D6-97C2-CF95051C2B37}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62E3ECD6-B146-4072-A5FF-DA34DDBC6681}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDEF7A6B-DABF-4934-83E1-967FCB2D7948}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71DF8E51-F87F-412A-BA7B-3623376C6A25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A034A217-13B4-493E-AD64-48A69B862D49}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F38B105C-4DED-43D6-97C2-CF95051C2B37}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A508E93-C3ED-4F11-A62A-42E76E99D688}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDEF7A6B-DABF-4934-83E1-967FCB2D7948}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE14F017-7177-487E-8055-B03B573E89C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A034A217-13B4-493E-AD64-48A69B862D49}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D26642D-A51C-46DD-B9D9-A07A94E6F521}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A508E93-C3ED-4F11-A62A-42E76E99D688}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2747A802-0C44-4467-8BF8-9FD3D314334B}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1356,291 +1356,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE14F017-7177-487E-8055-B03B573E89C2}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D26642D-A51C-46DD-B9D9-A07A94E6F521}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2747A802-0C44-4467-8BF8-9FD3D314334B}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1356,4 +1356,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F5FBDCA-2320-4275-8957-15C7A0AC1361}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04E0ACF1-D6B0-45B5-B7C5-A833E853E591}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFBFCFC2-9C1D-404F-B8F9-7F8EA354655A}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F5FBDCA-2320-4275-8957-15C7A0AC1361}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80A53FE3-B34A-4600-A6C4-7D526958F85A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04E0ACF1-D6B0-45B5-B7C5-A833E853E591}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EBB4F9A-7CCA-4B54-AB21-588C41C4A0CD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFBFCFC2-9C1D-404F-B8F9-7F8EA354655A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{815CDC16-172C-440B-B281-E3BC2B9EC454}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80A53FE3-B34A-4600-A6C4-7D526958F85A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E12D4D4D-CE2C-4DBE-92F4-E4B8446DC086}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EBB4F9A-7CCA-4B54-AB21-588C41C4A0CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A875A438-DB0E-4937-BFB8-8FB46D06BD84}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{815CDC16-172C-440B-B281-E3BC2B9EC454}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B60D341B-2D3B-44A6-8D49-E8FC01B2BCDF}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E12D4D4D-CE2C-4DBE-92F4-E4B8446DC086}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B626F70-919C-47D9-82C5-785D29D771E1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A875A438-DB0E-4937-BFB8-8FB46D06BD84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{037B21B1-94C9-4076-8A5E-640D08F7A503}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B60D341B-2D3B-44A6-8D49-E8FC01B2BCDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B9C9B37-CE4C-4F27-9DCB-48E77FB150DF}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B626F70-919C-47D9-82C5-785D29D771E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D30A093B-296B-414C-AD64-638DF6110675}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{037B21B1-94C9-4076-8A5E-640D08F7A503}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2894A2C9-2873-4EED-984D-018A7B2BCF78}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B9C9B37-CE4C-4F27-9DCB-48E77FB150DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF459C01-DC04-4395-B37B-FE54456667D1}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1634,13 +1634,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D30A093B-296B-414C-AD64-638DF6110675}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CEECDA0-B0E4-40E0-B1F3-4B5E6638FC28}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2894A2C9-2873-4EED-984D-018A7B2BCF78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{609440B4-DA08-46A4-A8FB-C4F5E3D80975}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF459C01-DC04-4395-B37B-FE54456667D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BC3BC13-CDC3-4B6B-9639-1AD15FD48641}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1356,291 +1356,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CEECDA0-B0E4-40E0-B1F3-4B5E6638FC28}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{609440B4-DA08-46A4-A8FB-C4F5E3D80975}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BC3BC13-CDC3-4B6B-9639-1AD15FD48641}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1356,4 +1356,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6448D56F-B848-4F26-96CD-AD0E99AC6148}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0815E6FF-A8C5-4FE1-B0A1-5EC6FB9CC2C3}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5A9C4B7-DFFF-402B-ACCC-FAFE6C55DD08}"/>
 </file>